--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col width="21.25" customWidth="1" style="2" min="1" max="1"/>
@@ -1421,6 +1421,31 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>多语言文本表</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TBLocalization</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Localization.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col width="21.25" customWidth="1" style="2" min="1" max="1"/>
@@ -1397,52 +1397,77 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>音效表</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>TBAudio</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>AudioData</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>AudioData.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>多语言文本表</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>TBLocalization</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>Localization</t>
         </is>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>Localization.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Level performance rating</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>TBLevelRating</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>LevelRating</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>LevelRating.xlsx</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>

--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>EnemyData.xlsx</t>
+          <t>EnemyData.xlsx,Levels/L01/EnemyData.xlsx,Levels/L02/EnemyData.xlsx,Levels/L03/EnemyData.xlsx,Levels/L04/EnemyData.xlsx,Levels/L05/EnemyData.xlsx,Levels/L06/EnemyData.xlsx,Levels/L07/EnemyData.xlsx,Levels/L08/EnemyData.xlsx,Levels/L09/EnemyData.xlsx,Levels/L10/EnemyData.xlsx,Levels/L11/EnemyData.xlsx,Levels/L12/EnemyData.xlsx,Levels/L13/EnemyData.xlsx,Levels/L14/EnemyData.xlsx,Levels/L15/EnemyData.xlsx,Levels/L16/EnemyData.xlsx,Levels/L17/EnemyData.xlsx,Levels/L18/EnemyData.xlsx,Levels/L19/EnemyData.xlsx,Levels/L20/EnemyData.xlsx,Levels/L21/EnemyData.xlsx,Levels/L22/EnemyData.xlsx,Levels/L23/EnemyData.xlsx,Levels/L24/EnemyData.xlsx,Levels/L25/EnemyData.xlsx,Levels/L26/EnemyData.xlsx,Levels/L27/EnemyData.xlsx,Levels/L28/EnemyData.xlsx,Levels/L29/EnemyData.xlsx,Levels/L30/EnemyData.xlsx</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>RoundData.xlsx</t>
+          <t>Levels/L01/RoundData.xlsx,Levels/L02/RoundData.xlsx,Levels/L03/RoundData.xlsx,Levels/L04/RoundData.xlsx,Levels/L05/RoundData.xlsx,Levels/L06/RoundData.xlsx,Levels/L07/RoundData.xlsx,Levels/L08/RoundData.xlsx,Levels/L09/RoundData.xlsx,Levels/L10/RoundData.xlsx,Levels/L11/RoundData.xlsx,Levels/L12/RoundData.xlsx,Levels/L13/RoundData.xlsx,Levels/L14/RoundData.xlsx,Levels/L15/RoundData.xlsx,Levels/L16/RoundData.xlsx,Levels/L17/RoundData.xlsx,Levels/L18/RoundData.xlsx,Levels/L19/RoundData.xlsx,Levels/L20/RoundData.xlsx,Levels/L21/RoundData.xlsx,Levels/L22/RoundData.xlsx,Levels/L23/RoundData.xlsx,Levels/L24/RoundData.xlsx,Levels/L25/RoundData.xlsx,Levels/L26/RoundData.xlsx,Levels/L27/RoundData.xlsx,Levels/L28/RoundData.xlsx,Levels/L29/RoundData.xlsx,Levels/L30/RoundData.xlsx</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>EnemyList.xlsx</t>
+          <t>Levels/L01/EnemyList.xlsx,Levels/L02/EnemyList.xlsx,Levels/L03/EnemyList.xlsx,Levels/L04/EnemyList.xlsx,Levels/L05/EnemyList.xlsx,Levels/L06/EnemyList.xlsx,Levels/L07/EnemyList.xlsx,Levels/L08/EnemyList.xlsx,Levels/L09/EnemyList.xlsx,Levels/L10/EnemyList.xlsx,Levels/L11/EnemyList.xlsx,Levels/L12/EnemyList.xlsx,Levels/L13/EnemyList.xlsx,Levels/L14/EnemyList.xlsx,Levels/L15/EnemyList.xlsx,Levels/L16/EnemyList.xlsx,Levels/L17/EnemyList.xlsx,Levels/L18/EnemyList.xlsx,Levels/L19/EnemyList.xlsx,Levels/L20/EnemyList.xlsx,Levels/L21/EnemyList.xlsx,Levels/L22/EnemyList.xlsx,Levels/L23/EnemyList.xlsx,Levels/L24/EnemyList.xlsx,Levels/L25/EnemyList.xlsx,Levels/L26/EnemyList.xlsx,Levels/L27/EnemyList.xlsx,Levels/L28/EnemyList.xlsx,Levels/L29/EnemyList.xlsx,Levels/L30/EnemyList.xlsx</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>SceneInfo.xlsx</t>
+          <t>Levels/L01/SceneInfo.xlsx,Levels/L02/SceneInfo.xlsx,Levels/L03/SceneInfo.xlsx,Levels/L04/SceneInfo.xlsx,Levels/L05/SceneInfo.xlsx,Levels/L06/SceneInfo.xlsx,Levels/L07/SceneInfo.xlsx,Levels/L08/SceneInfo.xlsx,Levels/L09/SceneInfo.xlsx,Levels/L10/SceneInfo.xlsx,Levels/L11/SceneInfo.xlsx,Levels/L12/SceneInfo.xlsx,Levels/L13/SceneInfo.xlsx,Levels/L14/SceneInfo.xlsx,Levels/L15/SceneInfo.xlsx,Levels/L16/SceneInfo.xlsx,Levels/L17/SceneInfo.xlsx,Levels/L18/SceneInfo.xlsx,Levels/L19/SceneInfo.xlsx,Levels/L20/SceneInfo.xlsx,Levels/L21/SceneInfo.xlsx,Levels/L22/SceneInfo.xlsx,Levels/L23/SceneInfo.xlsx,Levels/L24/SceneInfo.xlsx,Levels/L25/SceneInfo.xlsx,Levels/L26/SceneInfo.xlsx,Levels/L27/SceneInfo.xlsx,Levels/L28/SceneInfo.xlsx,Levels/L29/SceneInfo.xlsx,Levels/L30/SceneInfo.xlsx</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>LevelMap.xlsx</t>
+          <t>Levels/L01/LevelMap.xlsx,Levels/L02/LevelMap.xlsx,Levels/L03/LevelMap.xlsx,Levels/L04/LevelMap.xlsx,Levels/L05/LevelMap.xlsx,Levels/L06/LevelMap.xlsx,Levels/L07/LevelMap.xlsx,Levels/L08/LevelMap.xlsx,Levels/L09/LevelMap.xlsx,Levels/L10/LevelMap.xlsx,Levels/L11/LevelMap.xlsx,Levels/L12/LevelMap.xlsx,Levels/L13/LevelMap.xlsx,Levels/L14/LevelMap.xlsx,Levels/L15/LevelMap.xlsx,Levels/L16/LevelMap.xlsx,Levels/L17/LevelMap.xlsx,Levels/L18/LevelMap.xlsx,Levels/L19/LevelMap.xlsx,Levels/L20/LevelMap.xlsx,Levels/L21/LevelMap.xlsx,Levels/L22/LevelMap.xlsx,Levels/L23/LevelMap.xlsx,Levels/L24/LevelMap.xlsx,Levels/L25/LevelMap.xlsx,Levels/L26/LevelMap.xlsx,Levels/L27/LevelMap.xlsx,Levels/L28/LevelMap.xlsx,Levels/L29/LevelMap.xlsx,Levels/L30/LevelMap.xlsx</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>LevelRating.xlsx</t>
+          <t>Levels/L01/LevelRating.xlsx,Levels/L02/LevelRating.xlsx,Levels/L03/LevelRating.xlsx,Levels/L04/LevelRating.xlsx,Levels/L05/LevelRating.xlsx,Levels/L06/LevelRating.xlsx,Levels/L07/LevelRating.xlsx,Levels/L08/LevelRating.xlsx,Levels/L09/LevelRating.xlsx,Levels/L10/LevelRating.xlsx,Levels/L11/LevelRating.xlsx,Levels/L12/LevelRating.xlsx,Levels/L13/LevelRating.xlsx,Levels/L14/LevelRating.xlsx,Levels/L15/LevelRating.xlsx,Levels/L16/LevelRating.xlsx,Levels/L17/LevelRating.xlsx,Levels/L18/LevelRating.xlsx,Levels/L19/LevelRating.xlsx,Levels/L20/LevelRating.xlsx,Levels/L21/LevelRating.xlsx,Levels/L22/LevelRating.xlsx,Levels/L23/LevelRating.xlsx,Levels/L24/LevelRating.xlsx,Levels/L25/LevelRating.xlsx,Levels/L26/LevelRating.xlsx,Levels/L27/LevelRating.xlsx,Levels/L28/LevelRating.xlsx,Levels/L29/LevelRating.xlsx,Levels/L30/LevelRating.xlsx</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1396,31 +1396,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>音效表</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>TBAudio</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>AudioData</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>AudioData.xlsx</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>

--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col width="21.25" customWidth="1" style="2" min="1" max="1"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>EnemyData.xlsx,Levels/L01/EnemyData.xlsx,Levels/L02/EnemyData.xlsx,Levels/L03/EnemyData.xlsx,Levels/L04/EnemyData.xlsx,Levels/L05/EnemyData.xlsx,Levels/L06/EnemyData.xlsx,Levels/L07/EnemyData.xlsx,Levels/L08/EnemyData.xlsx,Levels/L09/EnemyData.xlsx,Levels/L10/EnemyData.xlsx,Levels/L11/EnemyData.xlsx,Levels/L12/EnemyData.xlsx,Levels/L13/EnemyData.xlsx,Levels/L14/EnemyData.xlsx,Levels/L15/EnemyData.xlsx,Levels/L16/EnemyData.xlsx,Levels/L17/EnemyData.xlsx,Levels/L18/EnemyData.xlsx,Levels/L19/EnemyData.xlsx,Levels/L20/EnemyData.xlsx,Levels/L21/EnemyData.xlsx,Levels/L22/EnemyData.xlsx,Levels/L23/EnemyData.xlsx,Levels/L24/EnemyData.xlsx,Levels/L25/EnemyData.xlsx,Levels/L26/EnemyData.xlsx,Levels/L27/EnemyData.xlsx,Levels/L28/EnemyData.xlsx,Levels/L29/EnemyData.xlsx,Levels/L30/EnemyData.xlsx</t>
+          <t>Levels/L01/EnemyData.xlsx,Levels/L02/EnemyData.xlsx,Levels/L03/EnemyData.xlsx,Levels/L04/EnemyData.xlsx,Levels/L05/EnemyData.xlsx,Levels/L06/EnemyData.xlsx,Levels/L07/EnemyData.xlsx,Levels/L08/EnemyData.xlsx,Levels/L09/EnemyData.xlsx,Levels/L10/EnemyData.xlsx,Levels/L11/EnemyData.xlsx,Levels/L12/EnemyData.xlsx,Levels/L13/EnemyData.xlsx,Levels/L14/EnemyData.xlsx,Levels/L15/EnemyData.xlsx,Levels/L16/EnemyData.xlsx,Levels/L17/EnemyData.xlsx,Levels/L18/EnemyData.xlsx,Levels/L19/EnemyData.xlsx,Levels/L20/EnemyData.xlsx,Levels/L21/EnemyData.xlsx,Levels/L22/EnemyData.xlsx,Levels/L23/EnemyData.xlsx,Levels/L24/EnemyData.xlsx,Levels/L25/EnemyData.xlsx,Levels/L26/EnemyData.xlsx,Levels/L27/EnemyData.xlsx,Levels/L28/EnemyData.xlsx,Levels/L29/EnemyData.xlsx,Levels/L30/EnemyData.xlsx</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>TowerInfo.xlsx</t>
+          <t>Levels/L01/TowerInfo.xlsx,Levels/L02/TowerInfo.xlsx,Levels/L03/TowerInfo.xlsx,Levels/L04/TowerInfo.xlsx,Levels/L05/TowerInfo.xlsx,Levels/L06/TowerInfo.xlsx,Levels/L07/TowerInfo.xlsx,Levels/L08/TowerInfo.xlsx,Levels/L09/TowerInfo.xlsx,Levels/L10/TowerInfo.xlsx,Levels/L11/TowerInfo.xlsx,Levels/L12/TowerInfo.xlsx,Levels/L13/TowerInfo.xlsx,Levels/L14/TowerInfo.xlsx,Levels/L15/TowerInfo.xlsx,Levels/L16/TowerInfo.xlsx,Levels/L17/TowerInfo.xlsx,Levels/L18/TowerInfo.xlsx,Levels/L19/TowerInfo.xlsx,Levels/L20/TowerInfo.xlsx,Levels/L21/TowerInfo.xlsx,Levels/L22/TowerInfo.xlsx,Levels/L23/TowerInfo.xlsx,Levels/L24/TowerInfo.xlsx,Levels/L25/TowerInfo.xlsx,Levels/L26/TowerInfo.xlsx,Levels/L27/TowerInfo.xlsx,Levels/L28/TowerInfo.xlsx,Levels/L29/TowerInfo.xlsx,Levels/L30/TowerInfo.xlsx</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>BulletData.xlsx</t>
+          <t>Levels/L01/BulletData.xlsx,Levels/L02/BulletData.xlsx,Levels/L03/BulletData.xlsx,Levels/L04/BulletData.xlsx,Levels/L05/BulletData.xlsx,Levels/L06/BulletData.xlsx,Levels/L07/BulletData.xlsx,Levels/L08/BulletData.xlsx,Levels/L09/BulletData.xlsx,Levels/L10/BulletData.xlsx,Levels/L11/BulletData.xlsx,Levels/L12/BulletData.xlsx,Levels/L13/BulletData.xlsx,Levels/L14/BulletData.xlsx,Levels/L15/BulletData.xlsx,Levels/L16/BulletData.xlsx,Levels/L17/BulletData.xlsx,Levels/L18/BulletData.xlsx,Levels/L19/BulletData.xlsx,Levels/L20/BulletData.xlsx,Levels/L21/BulletData.xlsx,Levels/L22/BulletData.xlsx,Levels/L23/BulletData.xlsx,Levels/L24/BulletData.xlsx,Levels/L25/BulletData.xlsx,Levels/L26/BulletData.xlsx,Levels/L27/BulletData.xlsx,Levels/L28/BulletData.xlsx,Levels/L29/BulletData.xlsx,Levels/L30/BulletData.xlsx</t>
         </is>
       </c>
     </row>
@@ -1444,6 +1444,33 @@
       <c r="E14" s="0" t="inlineStr">
         <is>
           <t>Levels/L01/LevelRating.xlsx,Levels/L02/LevelRating.xlsx,Levels/L03/LevelRating.xlsx,Levels/L04/LevelRating.xlsx,Levels/L05/LevelRating.xlsx,Levels/L06/LevelRating.xlsx,Levels/L07/LevelRating.xlsx,Levels/L08/LevelRating.xlsx,Levels/L09/LevelRating.xlsx,Levels/L10/LevelRating.xlsx,Levels/L11/LevelRating.xlsx,Levels/L12/LevelRating.xlsx,Levels/L13/LevelRating.xlsx,Levels/L14/LevelRating.xlsx,Levels/L15/LevelRating.xlsx,Levels/L16/LevelRating.xlsx,Levels/L17/LevelRating.xlsx,Levels/L18/LevelRating.xlsx,Levels/L19/LevelRating.xlsx,Levels/L20/LevelRating.xlsx,Levels/L21/LevelRating.xlsx,Levels/L22/LevelRating.xlsx,Levels/L23/LevelRating.xlsx,Levels/L24/LevelRating.xlsx,Levels/L25/LevelRating.xlsx,Levels/L26/LevelRating.xlsx,Levels/L27/LevelRating.xlsx,Levels/L28/LevelRating.xlsx,Levels/L29/LevelRating.xlsx,Levels/L30/LevelRating.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>每关玩法常数（2026-10-30 从 Global 拆出）</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>TBLevelRules</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>LevelRules</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Levels/L01/LevelRules.xlsx,Levels/L02/LevelRules.xlsx,Levels/L03/LevelRules.xlsx,Levels/L04/LevelRules.xlsx,Levels/L05/LevelRules.xlsx,Levels/L06/LevelRules.xlsx,Levels/L07/LevelRules.xlsx,Levels/L08/LevelRules.xlsx,Levels/L09/LevelRules.xlsx,Levels/L10/LevelRules.xlsx,Levels/L11/LevelRules.xlsx,Levels/L12/LevelRules.xlsx,Levels/L13/LevelRules.xlsx,Levels/L14/LevelRules.xlsx,Levels/L15/LevelRules.xlsx,Levels/L16/LevelRules.xlsx,Levels/L17/LevelRules.xlsx,Levels/L18/LevelRules.xlsx,Levels/L19/LevelRules.xlsx,Levels/L20/LevelRules.xlsx,Levels/L21/LevelRules.xlsx,Levels/L22/LevelRules.xlsx,Levels/L23/LevelRules.xlsx,Levels/L24/LevelRules.xlsx,Levels/L25/LevelRules.xlsx,Levels/L26/LevelRules.xlsx,Levels/L27/LevelRules.xlsx,Levels/L28/LevelRules.xlsx,Levels/L29/LevelRules.xlsx,Levels/L30/LevelRules.xlsx</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/__tables__.xlsx
+++ b/Luban/Config/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col width="21.25" customWidth="1" style="2" min="1" max="1"/>
@@ -1425,50 +1425,25 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>Level performance rating</t>
+          <t>每关玩法常数（2026-10-30 从 Global 拆出）</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>TBLevelRating</t>
+          <t>TBLevelRules</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>LevelRating</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="b">
-        <v>1</v>
+          <t>LevelRules</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>Levels/L01/LevelRating.xlsx,Levels/L02/LevelRating.xlsx,Levels/L03/LevelRating.xlsx,Levels/L04/LevelRating.xlsx,Levels/L05/LevelRating.xlsx,Levels/L06/LevelRating.xlsx,Levels/L07/LevelRating.xlsx,Levels/L08/LevelRating.xlsx,Levels/L09/LevelRating.xlsx,Levels/L10/LevelRating.xlsx,Levels/L11/LevelRating.xlsx,Levels/L12/LevelRating.xlsx,Levels/L13/LevelRating.xlsx,Levels/L14/LevelRating.xlsx,Levels/L15/LevelRating.xlsx,Levels/L16/LevelRating.xlsx,Levels/L17/LevelRating.xlsx,Levels/L18/LevelRating.xlsx,Levels/L19/LevelRating.xlsx,Levels/L20/LevelRating.xlsx,Levels/L21/LevelRating.xlsx,Levels/L22/LevelRating.xlsx,Levels/L23/LevelRating.xlsx,Levels/L24/LevelRating.xlsx,Levels/L25/LevelRating.xlsx,Levels/L26/LevelRating.xlsx,Levels/L27/LevelRating.xlsx,Levels/L28/LevelRating.xlsx,Levels/L29/LevelRating.xlsx,Levels/L30/LevelRating.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>每关玩法常数（2026-10-30 从 Global 拆出）</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>TBLevelRules</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>LevelRules</t>
-        </is>
-      </c>
-      <c r="D15" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>Levels/L01/LevelRules.xlsx,Levels/L02/LevelRules.xlsx,Levels/L03/LevelRules.xlsx,Levels/L04/LevelRules.xlsx,Levels/L05/LevelRules.xlsx,Levels/L06/LevelRules.xlsx,Levels/L07/LevelRules.xlsx,Levels/L08/LevelRules.xlsx,Levels/L09/LevelRules.xlsx,Levels/L10/LevelRules.xlsx,Levels/L11/LevelRules.xlsx,Levels/L12/LevelRules.xlsx,Levels/L13/LevelRules.xlsx,Levels/L14/LevelRules.xlsx,Levels/L15/LevelRules.xlsx,Levels/L16/LevelRules.xlsx,Levels/L17/LevelRules.xlsx,Levels/L18/LevelRules.xlsx,Levels/L19/LevelRules.xlsx,Levels/L20/LevelRules.xlsx,Levels/L21/LevelRules.xlsx,Levels/L22/LevelRules.xlsx,Levels/L23/LevelRules.xlsx,Levels/L24/LevelRules.xlsx,Levels/L25/LevelRules.xlsx,Levels/L26/LevelRules.xlsx,Levels/L27/LevelRules.xlsx,Levels/L28/LevelRules.xlsx,Levels/L29/LevelRules.xlsx,Levels/L30/LevelRules.xlsx</t>
         </is>
